--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,73 +453,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Petrobras</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Keywords</t>
+          <t>Oil, Offshore, Brent, Gas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ticker</t>
+          <t>PETR4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Petrobras</t>
+          <t>Vale</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Mining</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oil, Offshore, Brent, Gas</t>
+          <t>Iron Ore, China, Nickel</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>VALE3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vale</t>
+          <t>Itaú Unibanco</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mining</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iron Ore, China, Nickel</t>
+          <t>Credit, Pix, Digital Banking</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>ITUB4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Itaú Unibanco</t>
+          <t>Banco do Brasil</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -529,19 +529,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Credit, Pix, Digital Banking</t>
+          <t>Agribusiness, Credit, Government</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ITUB4</t>
+          <t>BBAS3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Banco do Brasil</t>
+          <t>Bradesco</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,142 +551,120 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Agribusiness, Credit, Government</t>
+          <t>Insurance, Banking, Digital</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BBAS3</t>
+          <t>BBDC4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bradesco</t>
+          <t>Embraer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Aerospace</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Insurance, Banking, Digital</t>
+          <t>Aircraft, Defense, Aviation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>EMBJ3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Suzano</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aerospace</t>
+          <t>Pulp &amp; Paper</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aircraft, Defense, Aviation</t>
+          <t>Cellulose, Forestry, ESG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EMBR3</t>
+          <t>SUZB3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Suzano</t>
+          <t>WEG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pulp &amp; Paper</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cellulose, Forestry, ESG</t>
+          <t>Electric Motors, Automation</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>WEGE3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WEG</t>
+          <t>Gerdau</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Electric Motors, Automation</t>
+          <t>Steel, Construction, Rebar</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>GGBR4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gerdau</t>
+          <t>Ambev</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Steel, Construction, Rebar</t>
+          <t>Beer, Beverage, AB InBev</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>GGBR4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Ambev</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Consumer</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Beer, Beverage, AB InBev</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>ABEV3</t>
         </is>
